--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 13:21:23 | Total Test Cases: 0</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 13:48:44 | Total Test Cases: 0</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 13:21:23</t>
+          <t>2026-07-27 13:48:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 13:48:44 | Total Test Cases: 0</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:05:04 | Total Test Cases: 0</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 13:48:44</t>
+          <t>2026-07-27 14:05:04</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:05:04 | Total Test Cases: 0</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:11:17 | Total Test Cases: 0</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 14:05:04</t>
+          <t>2026-07-27 14:11:17</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Executed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Passed Tests" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Failed Tests" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Execution Metrics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Skipped Tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Execution Metrics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Defect Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:11:17 | Total Test Cases: 0</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-28 08:48:54 | Total Test Cases: 0</t>
         </is>
       </c>
     </row>
@@ -698,6 +700,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Latency / Exec Time (s)</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -821,7 +901,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 14:11:17</t>
+          <t>2026-07-28 08:48:54</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
